--- a/data/sars/pacific/tables/Pacific_2010_Appendix3.xlsx
+++ b/data/sars/pacific/tables/Pacific_2010_Appendix3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cfree/Dropbox/Chris/UCSB/projects/marine_mammals/us_sar_synthesis/data/sars/pacific/tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A09EF45-E2AC-C142-BF7D-EF928CA61544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA4CCB47-B013-C64B-9DEA-FE37614A1762}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="120" yWindow="500" windowWidth="33580" windowHeight="19720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="100" yWindow="500" windowWidth="33580" windowHeight="19720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table 1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="123">
   <si>
     <t>California sea lion</t>
   </si>
@@ -373,13 +373,22 @@
     <t>survey3</t>
   </si>
   <si>
-    <t>revised</t>
-  </si>
-  <si>
     <t>notes</t>
   </si>
   <si>
     <t>Rmax is missing in table. Value is from the SAR.</t>
+  </si>
+  <si>
+    <t>RF=0.5 in SAR; RF=0.4 was typo in table</t>
+  </si>
+  <si>
+    <t>revised_yn</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t>revision_yr</t>
   </si>
 </sst>
 </file>
@@ -390,7 +399,7 @@
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -409,13 +418,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <strike/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
@@ -447,7 +449,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -497,9 +499,6 @@
       <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
     </xf>
   </cellXfs>
@@ -806,7 +805,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R78"/>
+  <dimension ref="A1:S78"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="25.59765625" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="32.59765625" bestFit="1" customWidth="1"/>
@@ -822,11 +821,12 @@
     <col min="11" max="11" width="14.19921875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="13.3984375" bestFit="1" customWidth="1"/>
     <col min="13" max="15" width="13" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.3984375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="53.19921875" customWidth="1"/>
+    <col min="16" max="16" width="13.3984375" customWidth="1"/>
+    <col min="17" max="17" width="14.3984375" customWidth="1"/>
+    <col min="18" max="18" width="53.19921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="15" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>102</v>
       </c>
@@ -873,14 +873,17 @@
         <v>116</v>
       </c>
       <c r="P1" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="R1" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="Q1" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="R1" s="2"/>
-    </row>
-    <row r="2" spans="1:18" ht="15" x14ac:dyDescent="0.15">
+      <c r="S1" s="2"/>
+    </row>
+    <row r="2" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -930,9 +933,10 @@
         <v>2007</v>
       </c>
       <c r="Q2" s="4"/>
-      <c r="R2" s="5"/>
-    </row>
-    <row r="3" spans="1:18" ht="15" x14ac:dyDescent="0.15">
+      <c r="R2" s="4"/>
+      <c r="S2" s="5"/>
+    </row>
+    <row r="3" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
@@ -982,9 +986,10 @@
         <v>2005</v>
       </c>
       <c r="Q3" s="4"/>
-      <c r="R3" s="5"/>
-    </row>
-    <row r="4" spans="1:18" ht="15" x14ac:dyDescent="0.15">
+      <c r="R3" s="4"/>
+      <c r="S3" s="5"/>
+    </row>
+    <row r="4" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A4" s="6" t="s">
         <v>7</v>
       </c>
@@ -1029,10 +1034,13 @@
       <c r="P4" s="8">
         <v>2010</v>
       </c>
-      <c r="Q4" s="8"/>
-      <c r="R4" s="5"/>
-    </row>
-    <row r="5" spans="1:18" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q4" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="R4" s="8"/>
+      <c r="S4" s="5"/>
+    </row>
+    <row r="5" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A5" s="6" t="s">
         <v>7</v>
       </c>
@@ -1077,10 +1085,13 @@
       <c r="P5" s="8">
         <v>2010</v>
       </c>
-      <c r="Q5" s="8"/>
-      <c r="R5" s="7"/>
-    </row>
-    <row r="6" spans="1:18" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q5" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="R5" s="8"/>
+      <c r="S5" s="7"/>
+    </row>
+    <row r="6" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A6" s="1" t="s">
         <v>17</v>
       </c>
@@ -1130,9 +1141,10 @@
         <v>2007</v>
       </c>
       <c r="Q6" s="4"/>
-      <c r="R6" s="5"/>
-    </row>
-    <row r="7" spans="1:18" ht="15" x14ac:dyDescent="0.15">
+      <c r="R6" s="4"/>
+      <c r="S6" s="5"/>
+    </row>
+    <row r="7" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A7" s="1" t="s">
         <v>21</v>
       </c>
@@ -1178,9 +1190,10 @@
         <v>2000</v>
       </c>
       <c r="Q7" s="4"/>
-      <c r="R7" s="5"/>
-    </row>
-    <row r="8" spans="1:18" ht="15" x14ac:dyDescent="0.15">
+      <c r="R7" s="4"/>
+      <c r="S7" s="5"/>
+    </row>
+    <row r="8" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A8" s="6" t="s">
         <v>24</v>
       </c>
@@ -1229,10 +1242,13 @@
       <c r="P8" s="8">
         <v>2010</v>
       </c>
-      <c r="Q8" s="8"/>
-      <c r="R8" s="5"/>
-    </row>
-    <row r="9" spans="1:18" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q8" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="R8" s="8"/>
+      <c r="S8" s="5"/>
+    </row>
+    <row r="9" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A9" s="6" t="s">
         <v>26</v>
       </c>
@@ -1281,10 +1297,13 @@
       <c r="P9" s="8">
         <v>2010</v>
       </c>
-      <c r="Q9" s="8"/>
-      <c r="R9" s="7"/>
-    </row>
-    <row r="10" spans="1:18" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q9" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="R9" s="8"/>
+      <c r="S9" s="7"/>
+    </row>
+    <row r="10" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A10" s="1" t="s">
         <v>30</v>
       </c>
@@ -1306,8 +1325,8 @@
       <c r="G10" s="15">
         <v>0.04</v>
       </c>
-      <c r="H10" s="17">
-        <v>0.4</v>
+      <c r="H10">
+        <v>0.5</v>
       </c>
       <c r="I10" s="4">
         <v>15</v>
@@ -1334,9 +1353,12 @@
         <v>2009</v>
       </c>
       <c r="Q10" s="4"/>
-      <c r="R10" s="5"/>
-    </row>
-    <row r="11" spans="1:18" ht="15" x14ac:dyDescent="0.15">
+      <c r="R10" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="S10" s="5"/>
+    </row>
+    <row r="11" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A11" s="1" t="s">
         <v>30</v>
       </c>
@@ -1385,12 +1407,13 @@
       <c r="P11" s="4">
         <v>2009</v>
       </c>
-      <c r="Q11" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="R11" s="5"/>
-    </row>
-    <row r="12" spans="1:18" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q11" s="4"/>
+      <c r="R11" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="S11" s="5"/>
+    </row>
+    <row r="12" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A12" s="1" t="s">
         <v>30</v>
       </c>
@@ -1440,9 +1463,10 @@
         <v>2009</v>
       </c>
       <c r="Q12" s="4"/>
-      <c r="R12" s="5"/>
-    </row>
-    <row r="13" spans="1:18" ht="15" x14ac:dyDescent="0.15">
+      <c r="R12" s="4"/>
+      <c r="S12" s="5"/>
+    </row>
+    <row r="13" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A13" s="1" t="s">
         <v>30</v>
       </c>
@@ -1492,9 +1516,10 @@
         <v>2009</v>
       </c>
       <c r="Q13" s="4"/>
-      <c r="R13" s="5"/>
-    </row>
-    <row r="14" spans="1:18" ht="15" x14ac:dyDescent="0.15">
+      <c r="R13" s="4"/>
+      <c r="S13" s="5"/>
+    </row>
+    <row r="14" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A14" s="1" t="s">
         <v>30</v>
       </c>
@@ -1544,9 +1569,10 @@
         <v>2009</v>
       </c>
       <c r="Q14" s="4"/>
-      <c r="R14" s="7"/>
-    </row>
-    <row r="15" spans="1:18" ht="15" x14ac:dyDescent="0.15">
+      <c r="R14" s="4"/>
+      <c r="S14" s="7"/>
+    </row>
+    <row r="15" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A15" s="1" t="s">
         <v>30</v>
       </c>
@@ -1596,9 +1622,10 @@
         <v>2006</v>
       </c>
       <c r="Q15" s="4"/>
-      <c r="R15" s="5"/>
-    </row>
-    <row r="16" spans="1:18" ht="15" x14ac:dyDescent="0.15">
+      <c r="R15" s="4"/>
+      <c r="S15" s="5"/>
+    </row>
+    <row r="16" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A16" s="6" t="s">
         <v>39</v>
       </c>
@@ -1647,10 +1674,13 @@
       <c r="P16" s="8">
         <v>2010</v>
       </c>
-      <c r="Q16" s="8"/>
-      <c r="R16" s="5"/>
-    </row>
-    <row r="17" spans="1:18" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q16" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="R16" s="8"/>
+      <c r="S16" s="5"/>
+    </row>
+    <row r="17" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A17" s="6" t="s">
         <v>42</v>
       </c>
@@ -1699,10 +1729,13 @@
       <c r="P17" s="8">
         <v>2010</v>
       </c>
-      <c r="Q17" s="8"/>
-      <c r="R17" s="5"/>
-    </row>
-    <row r="18" spans="1:18" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q17" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="R17" s="8"/>
+      <c r="S17" s="5"/>
+    </row>
+    <row r="18" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A18" s="6" t="s">
         <v>43</v>
       </c>
@@ -1751,10 +1784,13 @@
       <c r="P18" s="8">
         <v>2010</v>
       </c>
-      <c r="Q18" s="8"/>
-      <c r="R18" s="7"/>
-    </row>
-    <row r="19" spans="1:18" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q18" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="R18" s="8"/>
+      <c r="S18" s="7"/>
+    </row>
+    <row r="19" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A19" s="1" t="s">
         <v>44</v>
       </c>
@@ -1803,10 +1839,11 @@
       <c r="P19" s="4">
         <v>2008</v>
       </c>
-      <c r="Q19" s="5"/>
+      <c r="Q19" s="4"/>
       <c r="R19" s="5"/>
-    </row>
-    <row r="20" spans="1:18" ht="15" x14ac:dyDescent="0.15">
+      <c r="S19" s="5"/>
+    </row>
+    <row r="20" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A20" s="6" t="s">
         <v>44</v>
       </c>
@@ -1855,10 +1892,13 @@
       <c r="P20" s="8">
         <v>2010</v>
       </c>
-      <c r="Q20" s="8"/>
-      <c r="R20" s="5"/>
-    </row>
-    <row r="21" spans="1:18" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q20" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="R20" s="8"/>
+      <c r="S20" s="5"/>
+    </row>
+    <row r="21" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A21" s="6" t="s">
         <v>48</v>
       </c>
@@ -1907,10 +1947,13 @@
       <c r="P21" s="8">
         <v>2010</v>
       </c>
-      <c r="Q21" s="8"/>
-      <c r="R21" s="5"/>
-    </row>
-    <row r="22" spans="1:18" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q21" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="R21" s="8"/>
+      <c r="S21" s="5"/>
+    </row>
+    <row r="22" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A22" s="6" t="s">
         <v>49</v>
       </c>
@@ -1959,10 +2002,13 @@
       <c r="P22" s="8">
         <v>2010</v>
       </c>
-      <c r="Q22" s="8"/>
-      <c r="R22" s="7"/>
-    </row>
-    <row r="23" spans="1:18" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q22" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="R22" s="8"/>
+      <c r="S22" s="7"/>
+    </row>
+    <row r="23" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A23" s="6" t="s">
         <v>50</v>
       </c>
@@ -2011,10 +2057,13 @@
       <c r="P23" s="8">
         <v>2010</v>
       </c>
-      <c r="Q23" s="8"/>
-      <c r="R23" s="5"/>
-    </row>
-    <row r="24" spans="1:18" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q23" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="R23" s="8"/>
+      <c r="S23" s="5"/>
+    </row>
+    <row r="24" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A24" s="6" t="s">
         <v>51</v>
       </c>
@@ -2063,10 +2112,13 @@
       <c r="P24" s="8">
         <v>2010</v>
       </c>
-      <c r="Q24" s="8"/>
-      <c r="R24" s="5"/>
-    </row>
-    <row r="25" spans="1:18" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q24" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="R24" s="8"/>
+      <c r="S24" s="5"/>
+    </row>
+    <row r="25" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A25" s="6" t="s">
         <v>52</v>
       </c>
@@ -2115,10 +2167,13 @@
       <c r="P25" s="8">
         <v>2010</v>
       </c>
-      <c r="Q25" s="8"/>
-      <c r="R25" s="5"/>
-    </row>
-    <row r="26" spans="1:18" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q25" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="R25" s="8"/>
+      <c r="S25" s="5"/>
+    </row>
+    <row r="26" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A26" s="6" t="s">
         <v>52</v>
       </c>
@@ -2167,10 +2222,13 @@
       <c r="P26" s="8">
         <v>2010</v>
       </c>
-      <c r="Q26" s="8"/>
-      <c r="R26" s="7"/>
-    </row>
-    <row r="27" spans="1:18" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q26" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="R26" s="8"/>
+      <c r="S26" s="7"/>
+    </row>
+    <row r="27" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A27" s="6" t="s">
         <v>56</v>
       </c>
@@ -2193,7 +2251,7 @@
         <v>0.04</v>
       </c>
       <c r="H27" s="11">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="I27" s="11">
         <v>4.5999999999999996</v>
@@ -2219,10 +2277,15 @@
       <c r="P27" s="8">
         <v>2010</v>
       </c>
-      <c r="Q27" s="8"/>
-      <c r="R27" s="5"/>
-    </row>
-    <row r="28" spans="1:18" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q27" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="R27" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="S27" s="5"/>
+    </row>
+    <row r="28" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A28" s="6" t="s">
         <v>57</v>
       </c>
@@ -2271,10 +2334,13 @@
       <c r="P28" s="8">
         <v>2010</v>
       </c>
-      <c r="Q28" s="8"/>
-      <c r="R28" s="5"/>
-    </row>
-    <row r="29" spans="1:18" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q28" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="R28" s="8"/>
+      <c r="S28" s="5"/>
+    </row>
+    <row r="29" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A29" s="6" t="s">
         <v>58</v>
       </c>
@@ -2323,10 +2389,13 @@
       <c r="P29" s="8">
         <v>2010</v>
       </c>
-      <c r="Q29" s="8"/>
-      <c r="R29" s="5"/>
-    </row>
-    <row r="30" spans="1:18" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q29" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="R29" s="8"/>
+      <c r="S29" s="5"/>
+    </row>
+    <row r="30" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A30" s="6" t="s">
         <v>59</v>
       </c>
@@ -2375,10 +2444,13 @@
       <c r="P30" s="8">
         <v>2010</v>
       </c>
-      <c r="Q30" s="8"/>
-      <c r="R30" s="5"/>
-    </row>
-    <row r="31" spans="1:18" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q30" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="R30" s="8"/>
+      <c r="S30" s="5"/>
+    </row>
+    <row r="31" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A31" s="6" t="s">
         <v>60</v>
       </c>
@@ -2427,10 +2499,13 @@
       <c r="P31" s="8">
         <v>2010</v>
       </c>
-      <c r="Q31" s="8"/>
-      <c r="R31" s="7"/>
-    </row>
-    <row r="32" spans="1:18" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q31" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="R31" s="8"/>
+      <c r="S31" s="7"/>
+    </row>
+    <row r="32" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A32" s="6" t="s">
         <v>61</v>
       </c>
@@ -2479,10 +2554,13 @@
       <c r="P32" s="8">
         <v>2010</v>
       </c>
-      <c r="Q32" s="8"/>
-      <c r="R32" s="5"/>
-    </row>
-    <row r="33" spans="1:18" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q32" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="R32" s="8"/>
+      <c r="S32" s="5"/>
+    </row>
+    <row r="33" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A33" s="6" t="s">
         <v>62</v>
       </c>
@@ -2531,10 +2609,13 @@
       <c r="P33" s="8">
         <v>2010</v>
       </c>
-      <c r="Q33" s="8"/>
-      <c r="R33" s="5"/>
-    </row>
-    <row r="34" spans="1:18" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q33" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="R33" s="8"/>
+      <c r="S33" s="5"/>
+    </row>
+    <row r="34" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A34" s="6" t="s">
         <v>63</v>
       </c>
@@ -2583,10 +2664,13 @@
       <c r="P34" s="8">
         <v>2010</v>
       </c>
-      <c r="Q34" s="8"/>
-      <c r="R34" s="5"/>
-    </row>
-    <row r="35" spans="1:18" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q34" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="R34" s="8"/>
+      <c r="S34" s="5"/>
+    </row>
+    <row r="35" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A35" s="6" t="s">
         <v>66</v>
       </c>
@@ -2635,10 +2719,13 @@
       <c r="P35" s="8">
         <v>2010</v>
       </c>
-      <c r="Q35" s="8"/>
-      <c r="R35" s="7"/>
-    </row>
-    <row r="36" spans="1:18" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q35" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="R35" s="8"/>
+      <c r="S35" s="7"/>
+    </row>
+    <row r="36" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A36" s="6" t="s">
         <v>68</v>
       </c>
@@ -2687,10 +2774,13 @@
       <c r="P36" s="8">
         <v>2010</v>
       </c>
-      <c r="Q36" s="8"/>
-      <c r="R36" s="5"/>
-    </row>
-    <row r="37" spans="1:18" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q36" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="R36" s="8"/>
+      <c r="S36" s="5"/>
+    </row>
+    <row r="37" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A37" s="6" t="s">
         <v>69</v>
       </c>
@@ -2739,10 +2829,13 @@
       <c r="P37" s="8">
         <v>2010</v>
       </c>
-      <c r="Q37" s="8"/>
-      <c r="R37" s="5"/>
-    </row>
-    <row r="38" spans="1:18" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q37" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="R37" s="8"/>
+      <c r="S37" s="5"/>
+    </row>
+    <row r="38" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A38" s="6" t="s">
         <v>70</v>
       </c>
@@ -2791,10 +2884,13 @@
       <c r="P38" s="8">
         <v>2010</v>
       </c>
-      <c r="Q38" s="8"/>
-      <c r="R38" s="5"/>
-    </row>
-    <row r="39" spans="1:18" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q38" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="R38" s="8"/>
+      <c r="S38" s="5"/>
+    </row>
+    <row r="39" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A39" s="6" t="s">
         <v>71</v>
       </c>
@@ -2839,10 +2935,13 @@
       <c r="P39" s="8">
         <v>2010</v>
       </c>
-      <c r="Q39" s="8"/>
-      <c r="R39" s="7"/>
-    </row>
-    <row r="40" spans="1:18" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q39" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="R39" s="8"/>
+      <c r="S39" s="7"/>
+    </row>
+    <row r="40" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A40" s="6" t="s">
         <v>71</v>
       </c>
@@ -2891,10 +2990,13 @@
       <c r="P40" s="8">
         <v>2010</v>
       </c>
-      <c r="Q40" s="8"/>
-      <c r="R40" s="5"/>
-    </row>
-    <row r="41" spans="1:18" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q40" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="R40" s="8"/>
+      <c r="S40" s="5"/>
+    </row>
+    <row r="41" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A41" s="6" t="s">
         <v>43</v>
       </c>
@@ -2939,10 +3041,13 @@
       <c r="P41" s="8">
         <v>2010</v>
       </c>
-      <c r="Q41" s="8"/>
-      <c r="R41" s="7"/>
-    </row>
-    <row r="42" spans="1:18" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q41" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="R41" s="8"/>
+      <c r="S41" s="7"/>
+    </row>
+    <row r="42" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A42" s="6" t="s">
         <v>44</v>
       </c>
@@ -2987,10 +3092,13 @@
       <c r="P42" s="8">
         <v>2010</v>
       </c>
-      <c r="Q42" s="8"/>
-      <c r="R42" s="5"/>
-    </row>
-    <row r="43" spans="1:18" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q42" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="R42" s="8"/>
+      <c r="S42" s="5"/>
+    </row>
+    <row r="43" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A43" s="6" t="s">
         <v>44</v>
       </c>
@@ -3039,10 +3147,13 @@
       <c r="P43" s="8">
         <v>2010</v>
       </c>
-      <c r="Q43" s="8"/>
-      <c r="R43" s="5"/>
-    </row>
-    <row r="44" spans="1:18" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q43" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="R43" s="8"/>
+      <c r="S43" s="5"/>
+    </row>
+    <row r="44" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A44" s="6" t="s">
         <v>44</v>
       </c>
@@ -3091,10 +3202,13 @@
       <c r="P44" s="8">
         <v>2010</v>
       </c>
-      <c r="Q44" s="8"/>
-      <c r="R44" s="5"/>
-    </row>
-    <row r="45" spans="1:18" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q44" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="R44" s="8"/>
+      <c r="S44" s="5"/>
+    </row>
+    <row r="45" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A45" s="6" t="s">
         <v>44</v>
       </c>
@@ -3143,10 +3257,13 @@
       <c r="P45" s="8">
         <v>2010</v>
       </c>
-      <c r="Q45" s="8"/>
-      <c r="R45" s="7"/>
-    </row>
-    <row r="46" spans="1:18" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q45" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="R45" s="8"/>
+      <c r="S45" s="7"/>
+    </row>
+    <row r="46" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A46" s="6" t="s">
         <v>44</v>
       </c>
@@ -3195,10 +3312,13 @@
       <c r="P46" s="8">
         <v>2010</v>
       </c>
-      <c r="Q46" s="8"/>
-      <c r="R46" s="5"/>
-    </row>
-    <row r="47" spans="1:18" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q46" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="R46" s="8"/>
+      <c r="S46" s="5"/>
+    </row>
+    <row r="47" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A47" s="6" t="s">
         <v>78</v>
       </c>
@@ -3243,10 +3363,13 @@
       <c r="P47" s="8">
         <v>2010</v>
       </c>
-      <c r="Q47" s="8"/>
-      <c r="R47" s="5"/>
-    </row>
-    <row r="48" spans="1:18" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q47" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="R47" s="8"/>
+      <c r="S47" s="5"/>
+    </row>
+    <row r="48" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A48" s="6" t="s">
         <v>79</v>
       </c>
@@ -3293,10 +3416,13 @@
       <c r="P48" s="8">
         <v>2010</v>
       </c>
-      <c r="Q48" s="8"/>
-      <c r="R48" s="5"/>
-    </row>
-    <row r="49" spans="1:18" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q48" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="R48" s="8"/>
+      <c r="S48" s="5"/>
+    </row>
+    <row r="49" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A49" s="6" t="s">
         <v>79</v>
       </c>
@@ -3341,10 +3467,13 @@
       <c r="P49" s="8">
         <v>2010</v>
       </c>
-      <c r="Q49" s="8"/>
-      <c r="R49" s="5"/>
-    </row>
-    <row r="50" spans="1:18" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q49" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="R49" s="8"/>
+      <c r="S49" s="5"/>
+    </row>
+    <row r="50" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A50" s="6" t="s">
         <v>79</v>
       </c>
@@ -3393,10 +3522,13 @@
       <c r="P50" s="8">
         <v>2010</v>
       </c>
-      <c r="Q50" s="8"/>
-      <c r="R50" s="7"/>
-    </row>
-    <row r="51" spans="1:18" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q50" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="R50" s="8"/>
+      <c r="S50" s="7"/>
+    </row>
+    <row r="51" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A51" s="6" t="s">
         <v>79</v>
       </c>
@@ -3445,10 +3577,13 @@
       <c r="P51" s="8">
         <v>2010</v>
       </c>
-      <c r="Q51" s="8"/>
-      <c r="R51" s="5"/>
-    </row>
-    <row r="52" spans="1:18" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q51" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="R51" s="8"/>
+      <c r="S51" s="5"/>
+    </row>
+    <row r="52" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A52" s="6" t="s">
         <v>79</v>
       </c>
@@ -3497,10 +3632,13 @@
       <c r="P52" s="8">
         <v>2010</v>
       </c>
-      <c r="Q52" s="8"/>
-      <c r="R52" s="5"/>
-    </row>
-    <row r="53" spans="1:18" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q52" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="R52" s="8"/>
+      <c r="S52" s="5"/>
+    </row>
+    <row r="53" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A53" s="6" t="s">
         <v>79</v>
       </c>
@@ -3549,10 +3687,13 @@
       <c r="P53" s="8">
         <v>2010</v>
       </c>
-      <c r="Q53" s="8"/>
-      <c r="R53" s="5"/>
-    </row>
-    <row r="54" spans="1:18" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q53" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="R53" s="8"/>
+      <c r="S53" s="5"/>
+    </row>
+    <row r="54" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A54" s="6" t="s">
         <v>79</v>
       </c>
@@ -3601,10 +3742,13 @@
       <c r="P54" s="8">
         <v>2010</v>
       </c>
-      <c r="Q54" s="8"/>
-      <c r="R54" s="7"/>
-    </row>
-    <row r="55" spans="1:18" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q54" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="R54" s="8"/>
+      <c r="S54" s="7"/>
+    </row>
+    <row r="55" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A55" s="6" t="s">
         <v>48</v>
       </c>
@@ -3649,10 +3793,13 @@
       <c r="P55" s="8">
         <v>2010</v>
       </c>
-      <c r="Q55" s="8"/>
-      <c r="R55" s="5"/>
-    </row>
-    <row r="56" spans="1:18" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q55" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="R55" s="8"/>
+      <c r="S55" s="5"/>
+    </row>
+    <row r="56" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A56" s="6" t="s">
         <v>84</v>
       </c>
@@ -3697,10 +3844,13 @@
       <c r="P56" s="8">
         <v>2010</v>
       </c>
-      <c r="Q56" s="8"/>
-      <c r="R56" s="5"/>
-    </row>
-    <row r="57" spans="1:18" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q56" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="R56" s="8"/>
+      <c r="S56" s="5"/>
+    </row>
+    <row r="57" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A57" s="6" t="s">
         <v>85</v>
       </c>
@@ -3745,10 +3895,13 @@
       <c r="P57" s="8">
         <v>2010</v>
       </c>
-      <c r="Q57" s="8"/>
-      <c r="R57" s="5"/>
-    </row>
-    <row r="58" spans="1:18" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q57" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="R57" s="8"/>
+      <c r="S57" s="5"/>
+    </row>
+    <row r="58" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A58" s="6" t="s">
         <v>86</v>
       </c>
@@ -3793,10 +3946,13 @@
       <c r="P58" s="8">
         <v>2010</v>
       </c>
-      <c r="Q58" s="8"/>
-      <c r="R58" s="7"/>
-    </row>
-    <row r="59" spans="1:18" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q58" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="R58" s="8"/>
+      <c r="S58" s="7"/>
+    </row>
+    <row r="59" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A59" s="6" t="s">
         <v>87</v>
       </c>
@@ -3841,10 +3997,13 @@
       <c r="P59" s="8">
         <v>2010</v>
       </c>
-      <c r="Q59" s="8"/>
-      <c r="R59" s="5"/>
-    </row>
-    <row r="60" spans="1:18" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q59" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="R59" s="8"/>
+      <c r="S59" s="5"/>
+    </row>
+    <row r="60" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A60" s="6" t="s">
         <v>87</v>
       </c>
@@ -3889,10 +4048,13 @@
       <c r="P60" s="8">
         <v>2010</v>
       </c>
-      <c r="Q60" s="8"/>
-      <c r="R60" s="5"/>
-    </row>
-    <row r="61" spans="1:18" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q60" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="R60" s="8"/>
+      <c r="S60" s="5"/>
+    </row>
+    <row r="61" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A61" s="6" t="s">
         <v>87</v>
       </c>
@@ -3941,10 +4103,13 @@
       <c r="P61" s="8">
         <v>2010</v>
       </c>
-      <c r="Q61" s="8"/>
-      <c r="R61" s="5"/>
-    </row>
-    <row r="62" spans="1:18" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q61" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="R61" s="8"/>
+      <c r="S61" s="5"/>
+    </row>
+    <row r="62" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A62" s="6" t="s">
         <v>87</v>
       </c>
@@ -3993,10 +4158,13 @@
       <c r="P62" s="8">
         <v>2010</v>
       </c>
-      <c r="Q62" s="8"/>
-      <c r="R62" s="7"/>
-    </row>
-    <row r="63" spans="1:18" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q62" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="R62" s="8"/>
+      <c r="S62" s="7"/>
+    </row>
+    <row r="63" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A63" s="6" t="s">
         <v>52</v>
       </c>
@@ -4041,10 +4209,13 @@
       <c r="P63" s="8">
         <v>2010</v>
       </c>
-      <c r="Q63" s="8"/>
-      <c r="R63" s="5"/>
-    </row>
-    <row r="64" spans="1:18" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q63" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="R63" s="8"/>
+      <c r="S63" s="5"/>
+    </row>
+    <row r="64" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A64" s="6" t="s">
         <v>90</v>
       </c>
@@ -4089,10 +4260,13 @@
       <c r="P64" s="8">
         <v>2010</v>
       </c>
-      <c r="Q64" s="8"/>
-      <c r="R64" s="5"/>
-    </row>
-    <row r="65" spans="1:18" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q64" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="R64" s="8"/>
+      <c r="S64" s="5"/>
+    </row>
+    <row r="65" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A65" s="6" t="s">
         <v>91</v>
       </c>
@@ -4137,10 +4311,13 @@
       <c r="P65" s="8">
         <v>2010</v>
       </c>
-      <c r="Q65" s="8"/>
-      <c r="R65" s="5"/>
-    </row>
-    <row r="66" spans="1:18" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q65" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="R65" s="8"/>
+      <c r="S65" s="5"/>
+    </row>
+    <row r="66" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A66" s="6" t="s">
         <v>92</v>
       </c>
@@ -4185,10 +4362,13 @@
       <c r="P66" s="8">
         <v>2010</v>
       </c>
-      <c r="Q66" s="8"/>
-      <c r="R66" s="7"/>
-    </row>
-    <row r="67" spans="1:18" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q66" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="R66" s="8"/>
+      <c r="S66" s="7"/>
+    </row>
+    <row r="67" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A67" s="6" t="s">
         <v>59</v>
       </c>
@@ -4233,10 +4413,13 @@
       <c r="P67" s="8">
         <v>2010</v>
       </c>
-      <c r="Q67" s="8"/>
-      <c r="R67" s="5"/>
-    </row>
-    <row r="68" spans="1:18" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q67" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="R67" s="8"/>
+      <c r="S67" s="5"/>
+    </row>
+    <row r="68" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A68" s="6" t="s">
         <v>93</v>
       </c>
@@ -4281,10 +4464,13 @@
       <c r="P68" s="8">
         <v>2010</v>
       </c>
-      <c r="Q68" s="8"/>
-      <c r="R68" s="5"/>
-    </row>
-    <row r="69" spans="1:18" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q68" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="R68" s="8"/>
+      <c r="S68" s="5"/>
+    </row>
+    <row r="69" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A69" s="6" t="s">
         <v>61</v>
       </c>
@@ -4329,10 +4515,13 @@
       <c r="P69" s="8">
         <v>2010</v>
       </c>
-      <c r="Q69" s="8"/>
-      <c r="R69" s="5"/>
-    </row>
-    <row r="70" spans="1:18" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q69" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="R69" s="8"/>
+      <c r="S69" s="5"/>
+    </row>
+    <row r="70" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A70" s="6" t="s">
         <v>62</v>
       </c>
@@ -4377,10 +4566,13 @@
       <c r="P70" s="8">
         <v>2010</v>
       </c>
-      <c r="Q70" s="8"/>
-      <c r="R70" s="7"/>
-    </row>
-    <row r="71" spans="1:18" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q70" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="R70" s="8"/>
+      <c r="S70" s="7"/>
+    </row>
+    <row r="71" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A71" s="6" t="s">
         <v>66</v>
       </c>
@@ -4425,10 +4617,13 @@
       <c r="P71" s="8">
         <v>2010</v>
       </c>
-      <c r="Q71" s="8"/>
-      <c r="R71" s="5"/>
-    </row>
-    <row r="72" spans="1:18" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q71" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="R71" s="8"/>
+      <c r="S71" s="5"/>
+    </row>
+    <row r="72" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A72" s="6" t="s">
         <v>68</v>
       </c>
@@ -4473,10 +4668,13 @@
       <c r="P72" s="8">
         <v>2010</v>
       </c>
-      <c r="Q72" s="8"/>
-      <c r="R72" s="5"/>
-    </row>
-    <row r="73" spans="1:18" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q72" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="R72" s="8"/>
+      <c r="S72" s="5"/>
+    </row>
+    <row r="73" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A73" s="6" t="s">
         <v>95</v>
       </c>
@@ -4521,10 +4719,13 @@
       <c r="P73" s="8">
         <v>2010</v>
       </c>
-      <c r="Q73" s="8"/>
-      <c r="R73" s="5"/>
-    </row>
-    <row r="74" spans="1:18" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q73" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="R73" s="8"/>
+      <c r="S73" s="5"/>
+    </row>
+    <row r="74" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A74" s="6" t="s">
         <v>69</v>
       </c>
@@ -4569,10 +4770,13 @@
       <c r="P74" s="8">
         <v>2010</v>
       </c>
-      <c r="Q74" s="8"/>
-      <c r="R74" s="5"/>
-    </row>
-    <row r="75" spans="1:18" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q74" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="R74" s="8"/>
+      <c r="S74" s="5"/>
+    </row>
+    <row r="75" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A75" s="6" t="s">
         <v>70</v>
       </c>
@@ -4617,10 +4821,13 @@
       <c r="P75" s="8">
         <v>2010</v>
       </c>
-      <c r="Q75" s="8"/>
-      <c r="R75" s="7"/>
-    </row>
-    <row r="76" spans="1:18" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q75" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="R75" s="8"/>
+      <c r="S75" s="7"/>
+    </row>
+    <row r="76" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A76" s="1" t="s">
         <v>63</v>
       </c>
@@ -4670,9 +4877,10 @@
         <v>2009</v>
       </c>
       <c r="Q76" s="4"/>
-      <c r="R76" s="5"/>
-    </row>
-    <row r="77" spans="1:18" ht="15" x14ac:dyDescent="0.15">
+      <c r="R76" s="4"/>
+      <c r="S76" s="5"/>
+    </row>
+    <row r="77" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A77" s="1" t="s">
         <v>97</v>
       </c>
@@ -4722,9 +4930,10 @@
         <v>2008</v>
       </c>
       <c r="Q77" s="4"/>
-      <c r="R77" s="5"/>
-    </row>
-    <row r="78" spans="1:18" ht="15" x14ac:dyDescent="0.15">
+      <c r="R77" s="4"/>
+      <c r="S77" s="5"/>
+    </row>
+    <row r="78" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A78" s="1" t="s">
         <v>97</v>
       </c>
@@ -4774,7 +4983,8 @@
         <v>2008</v>
       </c>
       <c r="Q78" s="4"/>
-      <c r="R78" s="7"/>
+      <c r="R78" s="4"/>
+      <c r="S78" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
